--- a/FO-AL-001_LIMPIEZA_BLESS.xlsx
+++ b/FO-AL-001_LIMPIEZA_BLESS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\JUPYTERL\CAPA LIMPIEZA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EE0319-CCCD-4287-824A-C12B8CD2583A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A60A42A-089B-49B3-A625-384C8303F321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -420,7 +420,85 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -429,86 +507,8 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -869,7 +869,7 @@
   <cols>
     <col min="1" max="1" width="6.44921875" customWidth="1"/>
     <col min="2" max="2" width="9.796875" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12.19921875" customWidth="1"/>
     <col min="4" max="5" width="4.8984375" customWidth="1"/>
     <col min="6" max="6" width="5.09765625" customWidth="1"/>
     <col min="7" max="9" width="4.8984375" customWidth="1"/>
@@ -886,114 +886,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="18.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A1" s="22"/>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="23" t="s">
+      <c r="A1" s="35"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="17" t="s">
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="V1" s="17" t="s">
+      <c r="V1" s="30" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="18.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23" t="s">
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="18"/>
-      <c r="V2" s="18"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
     </row>
     <row r="3" spans="1:22" ht="18.5" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A3" s="22"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="19"/>
+      <c r="A3" s="35"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
     </row>
     <row r="4" spans="1:22" ht="31" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="14" t="s">
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="U4" s="15" t="s">
+      <c r="U4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="V4" s="15" t="s">
+      <c r="V4" s="12" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1043,21 +1043,21 @@
       <c r="V6" s="5"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.65">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="22"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="27"/>
+      <c r="E7" s="22"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="I7" s="27"/>
+      <c r="I7" s="22"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
@@ -1097,88 +1097,88 @@
       <c r="V8" s="5"/>
     </row>
     <row r="9" spans="1:22" ht="72" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="35" t="s">
+      <c r="C9" s="19"/>
+      <c r="D9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="35" t="s">
+      <c r="J9" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="35" t="s">
+      <c r="L9" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="35" t="s">
+      <c r="N9" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="O9" s="35" t="s">
+      <c r="O9" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="P9" s="35" t="s">
+      <c r="P9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="Q9" s="28" t="s">
+      <c r="Q9" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="R9" s="29"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="31" t="s">
+      <c r="R9" s="24"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="U9" s="31" t="s">
+      <c r="U9" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="V9" s="33" t="s">
+      <c r="V9" s="26" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A10" s="32"/>
-      <c r="B10" s="16" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
       <c r="Q10" s="8" t="s">
         <v>29</v>
       </c>
@@ -1188,9 +1188,9 @@
       <c r="S10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="T10" s="32"/>
-      <c r="U10" s="32"/>
-      <c r="V10" s="34"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="27"/>
     </row>
     <row r="11" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A11" s="1">
@@ -1999,67 +1999,67 @@
       <c r="V41" s="2"/>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.65">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-      <c r="J43" s="25"/>
-      <c r="K43" s="25"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="25"/>
-      <c r="N43" s="25"/>
-      <c r="O43" s="25"/>
-      <c r="P43" s="25"/>
-      <c r="Q43" s="25"/>
-      <c r="R43" s="25"/>
-      <c r="S43" s="25"/>
-      <c r="T43" s="25"/>
-      <c r="U43" s="25"/>
-      <c r="V43" s="25"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="20"/>
+      <c r="T43" s="20"/>
+      <c r="U43" s="20"/>
+      <c r="V43" s="20"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.65">
-      <c r="A44" s="25"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="25"/>
-      <c r="K44" s="25"/>
-      <c r="L44" s="25"/>
-      <c r="M44" s="25"/>
-      <c r="N44" s="25"/>
-      <c r="O44" s="25"/>
-      <c r="P44" s="25"/>
-      <c r="Q44" s="25"/>
-      <c r="R44" s="25"/>
-      <c r="S44" s="25"/>
-      <c r="T44" s="25"/>
-      <c r="U44" s="25"/>
-      <c r="V44" s="25"/>
+      <c r="A44" s="20"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="20"/>
+      <c r="T44" s="20"/>
+      <c r="U44" s="20"/>
+      <c r="V44" s="20"/>
     </row>
     <row r="56" spans="20:20" x14ac:dyDescent="0.65">
       <c r="T56" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
+  <mergeCells count="30">
+    <mergeCell ref="V1:V3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D2:T3"/>
+    <mergeCell ref="D1:T1"/>
+    <mergeCell ref="U1:U3"/>
+    <mergeCell ref="D4:S4"/>
     <mergeCell ref="A43:V44"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="D7:E7"/>
@@ -2076,12 +2076,13 @@
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="V1:V3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D2:T3"/>
-    <mergeCell ref="D1:T1"/>
-    <mergeCell ref="U1:U3"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
